--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714893</v>
+        <v>113714953</v>
       </c>
       <c r="B2" t="n">
-        <v>90316</v>
+        <v>90131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637764</v>
+        <v>638082</v>
       </c>
       <c r="R2" t="n">
-        <v>7033751</v>
+        <v>7033727</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113714895</v>
+        <v>113712690</v>
       </c>
       <c r="B3" t="n">
         <v>81944</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113714953</v>
+        <v>113712688</v>
       </c>
       <c r="B4" t="n">
-        <v>90131</v>
+        <v>90316</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638082</v>
+        <v>637764</v>
       </c>
       <c r="R4" t="n">
-        <v>7033727</v>
+        <v>7033751</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -962,12 +957,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113714929</v>
+        <v>113712728</v>
       </c>
       <c r="B5" t="n">
         <v>90131</v>

--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714953</v>
+        <v>113714929</v>
       </c>
       <c r="B2" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638082</v>
+        <v>637199</v>
       </c>
       <c r="R2" t="n">
-        <v>7033727</v>
+        <v>7033764</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712690</v>
+        <v>113714895</v>
       </c>
       <c r="B3" t="n">
         <v>81944</v>
@@ -890,7 +890,7 @@
         <v>113712688</v>
       </c>
       <c r="B4" t="n">
-        <v>90316</v>
+        <v>90320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113712728</v>
+        <v>113714953</v>
       </c>
       <c r="B5" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637199</v>
+        <v>638082</v>
       </c>
       <c r="R5" t="n">
-        <v>7033764</v>
+        <v>7033727</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714929</v>
+        <v>113714893</v>
       </c>
       <c r="B2" t="n">
-        <v>90135</v>
+        <v>90320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637199</v>
+        <v>637764</v>
       </c>
       <c r="R2" t="n">
-        <v>7033764</v>
+        <v>7033751</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113714895</v>
+        <v>113714929</v>
       </c>
       <c r="B3" t="n">
-        <v>81944</v>
+        <v>90135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637751</v>
+        <v>637199</v>
       </c>
       <c r="R3" t="n">
-        <v>7033753</v>
+        <v>7033764</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,12 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113712688</v>
+        <v>113712753</v>
       </c>
       <c r="B4" t="n">
-        <v>90320</v>
+        <v>90135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637764</v>
+        <v>638082</v>
       </c>
       <c r="R4" t="n">
-        <v>7033751</v>
+        <v>7033727</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -957,17 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113714953</v>
+        <v>113712690</v>
       </c>
       <c r="B5" t="n">
-        <v>90135</v>
+        <v>81944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638082</v>
+        <v>637751</v>
       </c>
       <c r="R5" t="n">
-        <v>7033727</v>
+        <v>7033753</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113714929</v>
+        <v>113712728</v>
       </c>
       <c r="B3" t="n">
         <v>90135</v>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113712753</v>
+        <v>113714895</v>
       </c>
       <c r="B4" t="n">
-        <v>90135</v>
+        <v>81944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638082</v>
+        <v>637751</v>
       </c>
       <c r="R4" t="n">
-        <v>7033727</v>
+        <v>7033753</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -962,12 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113712690</v>
+        <v>113712753</v>
       </c>
       <c r="B5" t="n">
-        <v>81944</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637751</v>
+        <v>638082</v>
       </c>
       <c r="R5" t="n">
-        <v>7033753</v>
+        <v>7033727</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714893</v>
+        <v>113712690</v>
       </c>
       <c r="B2" t="n">
-        <v>90320</v>
+        <v>81944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637764</v>
+        <v>637751</v>
       </c>
       <c r="R2" t="n">
-        <v>7033751</v>
+        <v>7033753</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712728</v>
+        <v>113712688</v>
       </c>
       <c r="B3" t="n">
-        <v>90135</v>
+        <v>90320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637199</v>
+        <v>637764</v>
       </c>
       <c r="R3" t="n">
-        <v>7033764</v>
+        <v>7033751</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,12 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113714895</v>
+        <v>113712753</v>
       </c>
       <c r="B4" t="n">
-        <v>81944</v>
+        <v>90135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637751</v>
+        <v>638082</v>
       </c>
       <c r="R4" t="n">
-        <v>7033753</v>
+        <v>7033727</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -962,12 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113712753</v>
+        <v>113712728</v>
       </c>
       <c r="B5" t="n">
         <v>90135</v>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638082</v>
+        <v>637199</v>
       </c>
       <c r="R5" t="n">
-        <v>7033727</v>
+        <v>7033764</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712690</v>
+        <v>113714929</v>
       </c>
       <c r="B2" t="n">
-        <v>81944</v>
+        <v>90135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637751</v>
+        <v>637199</v>
       </c>
       <c r="R2" t="n">
-        <v>7033753</v>
+        <v>7033764</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712688</v>
+        <v>113714895</v>
       </c>
       <c r="B3" t="n">
-        <v>90320</v>
+        <v>81944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637764</v>
+        <v>637751</v>
       </c>
       <c r="R3" t="n">
-        <v>7033751</v>
+        <v>7033753</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113712753</v>
+        <v>113712688</v>
       </c>
       <c r="B4" t="n">
-        <v>90135</v>
+        <v>90320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638082</v>
+        <v>637764</v>
       </c>
       <c r="R4" t="n">
-        <v>7033727</v>
+        <v>7033751</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -962,12 +957,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113712728</v>
+        <v>113712753</v>
       </c>
       <c r="B5" t="n">
         <v>90135</v>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637199</v>
+        <v>638082</v>
       </c>
       <c r="R5" t="n">
-        <v>7033764</v>
+        <v>7033727</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,200 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133758276</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hundberget, Hundberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>638162</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7033688</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133758302</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80474</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hundberget, Hundberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>638162</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7033688</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133758276</v>
+        <v>133758302</v>
       </c>
       <c r="B6" t="n">
-        <v>80438</v>
+        <v>80475</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1201,32 +1201,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133758302</v>
+        <v>133758276</v>
       </c>
       <c r="B7" t="n">
-        <v>80474</v>
+        <v>80439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>

--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1296,6 +1296,685 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133726282</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>637598</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7033766</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133726776</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91922</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>637406</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7033761</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133726606</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>637437</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7033788</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133724311</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>637722</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7033757</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133726435</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>637544</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7033775</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133735546</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>637485</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7033799</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133724412</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>637740</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7033750</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>133726776</v>
       </c>
       <c r="B9" t="n">
-        <v>91922</v>
+        <v>91926</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>133724311</v>
       </c>
       <c r="B11" t="n">
-        <v>91885</v>
+        <v>91889</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>133735546</v>
       </c>
       <c r="B13" t="n">
-        <v>91885</v>
+        <v>91889</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>133724412</v>
       </c>
       <c r="B14" t="n">
-        <v>91885</v>
+        <v>91889</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>133726776</v>
       </c>
       <c r="B9" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>133724311</v>
       </c>
       <c r="B11" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>133735546</v>
       </c>
       <c r="B13" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>133724412</v>
       </c>
       <c r="B14" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>133758302</v>
       </c>
       <c r="B6" t="n">
-        <v>80475</v>
+        <v>80489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>133758276</v>
       </c>
       <c r="B7" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>133726282</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>133726776</v>
       </c>
       <c r="B9" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>133726606</v>
       </c>
       <c r="B10" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>133724311</v>
       </c>
       <c r="B11" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>133726435</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>133735546</v>
       </c>
       <c r="B13" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>133724412</v>
       </c>
       <c r="B14" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>133758302</v>
       </c>
       <c r="B6" t="n">
-        <v>80489</v>
+        <v>80485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>133758276</v>
       </c>
       <c r="B7" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>133726282</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>133726776</v>
       </c>
       <c r="B9" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>133726606</v>
       </c>
       <c r="B10" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>133724311</v>
       </c>
       <c r="B11" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>133726435</v>
       </c>
       <c r="B12" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>133735546</v>
       </c>
       <c r="B13" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>133724412</v>
       </c>
       <c r="B14" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>133758302</v>
       </c>
       <c r="B6" t="n">
-        <v>80485</v>
+        <v>80486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>133758276</v>
       </c>
       <c r="B7" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>133726282</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>133726776</v>
       </c>
       <c r="B9" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>133726606</v>
       </c>
       <c r="B10" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>133724311</v>
       </c>
       <c r="B11" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>133726435</v>
       </c>
       <c r="B12" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>133735546</v>
       </c>
       <c r="B13" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>133724412</v>
       </c>
       <c r="B14" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 1285-2023 artfynd.xlsx
+++ b/artfynd/A 1285-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712688</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133737604</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133724368</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712728</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712753</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133724355</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1368,6 +1403,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133724519</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1465,6 +1505,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133726776</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1562,6 +1607,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729558</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1663,6 +1713,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712754</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712690</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1865,6 +1925,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712727</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1962,6 +2027,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133724311</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2059,6 +2129,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133724412</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2156,6 +2231,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133726490</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2253,6 +2333,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133726663</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2350,6 +2435,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133727051</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2447,6 +2537,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133735546</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2553,6 +2648,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712687</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2650,6 +2750,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133726282</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2747,6 +2852,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133726435</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2844,6 +2954,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133726606</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2941,6 +3056,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133735488</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3038,6 +3158,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133737141</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3139,6 +3264,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712684</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3236,6 +3366,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133726698</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3333,6 +3468,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133758276</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3430,6 +3570,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133726711</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3527,6 +3672,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133758302</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3640,6 +3790,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126410990</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3746,6 +3901,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712689</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3852,6 +4012,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712725</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3958,6 +4123,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712752</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4063,6 +4233,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133736632</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4169,8 +4344,50 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712731</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>